--- a/output/final_tags.xlsx
+++ b/output/final_tags.xlsx
@@ -12,8 +12,8 @@
     <sheet name="SUMMARY" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AUTO_ACCEPT'!$A$1:$O$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HUMAN_REVIEW'!$A$1:$R$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AUTO_ACCEPT'!$A$1:$O$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HUMAN_REVIEW'!$A$1:$R$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -172,10 +172,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -659,27 +659,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>K-V-201</t>
+          <t>2IN-GV-V273-11502X</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ETHANE GAS COMPRESSOR # 2,STATION-V</t>
+          <t>PIPING,FRM V-RV-207 D/S TO FLARE HDR</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>COMPRESSOR,GAS,ETHANE,1900TPD</t>
+          <t>PIPING,2IN,DP:19.6 TO 15.8BARG,DT:-50 TO 150DEG C</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1900TPD,10662RPM</t>
+          <t>2IN</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -724,39 +724,35 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>10IN-GV-V272-11502X</t>
+          <t>TT-202A</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>PIPING,FRM K-V-201 DISCH LN TO FLARE HDR</t>
+          <t>TEMPERATURE MEASUREMENT ON A LINE, LIKELY CONNECTED TO A CONTROL SYSTEM GIVEN THE DIAMOND SHAPE.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>PIPING,10IN,DP:19.6 TO 15.8BARG,DT:-50 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>10IN</t>
-        </is>
-      </c>
+          <t>TEMPERATURE TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -799,13 +795,13 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: TT-202A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -814,17 +810,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>LY-206</t>
+          <t>V-XS-239</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>LEVEL RELAY OR COMPUTE FUNCTION</t>
+          <t>SWITCH ASSOCIATED WITH PURGE COMPLETE SIGNAL</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -870,32 +866,32 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: LY-206 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-XS-239 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: upstream | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PIC-1466B</t>
+          <t>V-XA-237</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER, LIKELY PART OF A CONTROL LOOP, RECEIVING A SIGNAL FROM A LINE.</t>
+          <t>PURGE COMPLETE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
@@ -941,13 +937,13 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PIC-1466B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-XA-237 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: upstream | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -956,24 +952,20 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>V-FV-208</t>
+          <t>V-XS-238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FLOW CV,COMP ANTI SURGE VALVE,K-V-201</t>
+          <t>PURGE ALARM</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>VALVE,CONTROL,FLOW,6IN</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6IN</t>
-        </is>
-      </c>
+          <t>INSTRUMENT BUBBLE</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -1016,13 +1008,13 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-XS-238 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -1031,17 +1023,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>T-202A</t>
+          <t>T-202C</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER CONNECTED TO A LINE.</t>
+          <t>CONNECTED TO 12"X8" REDUCER</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
@@ -1087,13 +1079,13 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-202A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-202C | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -1102,17 +1094,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>V-XS-239</t>
+          <t>T-202B</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SWITCH CONNECTED TO INTERLOCK I-001</t>
+          <t>CONNECTED TO MAIN VERTICAL LINE</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SWITCH</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -1158,32 +1150,32 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-XS-239 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-202B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>V-XA-237</t>
+          <t>T-202A</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>PURGE COMPLETE</t>
+          <t>CONNECTED TO LINE WITH SPECTACLE BLIND</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -1229,35 +1221,39 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-XA-237 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-202A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>V-XS-238</t>
+          <t>K-V-201</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PURGE ALARM</t>
+          <t>ETHANE GAS COMPRESSOR # 2,STATION-V</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+          <t>COMPRESSOR,GAS,ETHANE,1900TPD</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1900TPD,10662RPM</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -1300,39 +1296,35 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-XS-238 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2IN-GV-V273-11502X</t>
+          <t>T-203A</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>PIPING,FRM V-RV-207 D/S TO FLARE HDR</t>
+          <t>TEMPERATURE MEASUREMENT ON COMPRESSOR LINE</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>PIPING,2IN,DP:19.6 TO 15.8BARG,DT:-50 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>2IN</t>
-        </is>
-      </c>
+          <t>TEMPERATURE TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -1375,13 +1367,13 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-203A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201 | FLOW: upstream | CONTROL_LOOP: CL-04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -1390,17 +1382,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>V-PAHH-211</t>
+          <t>KG-V-201</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE ALARM HIGH HIGH</t>
+          <t>GEAR BOX,ETH GAS COMPRESSOR,K-V-201</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>GEARBOX</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -1446,35 +1438,39 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PAHH-211 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>V-PIT-211</t>
+          <t>V-RV-208</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>CONNECTED TO PIPING LINE</t>
+          <t>SAFETY RELIEF VALVE,EGC D/L,K-V-201</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
+          <t>VALVE,RELIEF,65BARG,4X6IN</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>65BARG,4X6IN</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -1517,13 +1513,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIT-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -1532,17 +1528,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>T-202C</t>
+          <t>V-HS-214A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CONNECTED TO LINE</t>
+          <t>RCI TEST</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>HAND SWITCH</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1588,13 +1584,13 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-202C | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-HS-214A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1603,17 +1599,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>T-202B</t>
+          <t>V-HS-214A</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>CONNECTED TO LINE</t>
+          <t>RCI TEST</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>HAND SWITCH</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr"/>
@@ -1659,32 +1655,32 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-202B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-HS-214A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8IN</t>
+          <t>V-TAHH-212</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDICATES THE SIZE OF THE PIPE.</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1730,13 +1726,13 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '8IN' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TAHH-212 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -1745,17 +1741,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>T-203A</t>
+          <t>PAHH-211</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT ON COMPRESSOR LINE</t>
+          <t>PRESSURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>PRESSURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -1801,13 +1797,13 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-203A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PAHH-211 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -1816,17 +1812,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>T-203B</t>
+          <t>V-TIT-212</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT ON COMPRESSOR LINE</t>
+          <t>TEMP TX 2,COMP SUCTION GAS TEMP,K-V-201</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>TRANSMITTER,TEMPERATURE,INDICATING</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1872,32 +1868,32 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-203B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>KG-V-201</t>
+          <t>V-TIT-211</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>GEAR BOX,ETH GAS COMPRESSOR,K-V-201</t>
+          <t>TEMP TX 1,COMP SUCTION GAS TEMP,K-V-201</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>GEARBOX</t>
+          <t>TRANSMITTER,TEMPERATURE,INDICATING</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
@@ -1943,39 +1939,35 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ELECTRICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KM-V-201</t>
+          <t>PIT-212</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MOTOR,ETHANE COMPRESSOR,K-V-201</t>
+          <t>CONNECTED TO A HORIZONTAL PIPING LINE</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MOTOR,2600KW</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2600KW/1695RPM</t>
-        </is>
-      </c>
+          <t>PRESSURE INDICATING TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2018,39 +2010,35 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PIT-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>V-RV-208</t>
+          <t>T-203B</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>SAFETY RELIEF VALVE,EGC D/L,K-V-201</t>
+          <t>CONNECTED TO A LINE ABOVE</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>VALVE,RELIEF,65BARG,4X6IN</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>65BARG,4X6IN</t>
-        </is>
-      </c>
+          <t>LOGIC/INTERLOCK SYMBOL</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2093,39 +2081,35 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-203B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201 | FLOW: downstream | CONTROL_LOOP: CL-04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2248</t>
+          <t>V-TIT-213</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BV,COMPRSR D/L VENT,K-V-201 TO FLARE HDR</t>
+          <t>TEMPERATURE MEASUREMENT</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>VALVE,BALL,1IN</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1IN</t>
-        </is>
-      </c>
+          <t>TEMPERATURE INDICATING TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2168,32 +2152,32 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TIT-213 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>V-HS-214A</t>
+          <t>V-PAHH-213</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>RCI TEST</t>
+          <t>HIGH HIGH PRESSURE ALARM</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>HAND SWITCH</t>
+          <t>PRESSURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
@@ -2239,32 +2223,32 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-HS-214A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: KM-V-201 | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>V-HS-214A</t>
+          <t>V-TAHH-213</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>RCI TEST</t>
+          <t>HIGH HIGH TEMPERATURE ALARM</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>HAND SWITCH</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -2310,35 +2294,39 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-HS-214A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>ELECTRICAL</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>PALL-214</t>
+          <t>KM-V-201</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE ALARM LOW LOW</t>
+          <t>MOTOR,ETHANE COMPRESSOR,K-V-201</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE ALARM LOW LOW</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
+          <t>MOTOR,2600KW</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2600KW/1695RPM</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2381,32 +2369,32 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PALL-214 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>PI-211</t>
+          <t>V-PAHH-213</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATOR</t>
+          <t>PRESSURE ALARM HIGH HIGH ON A LINE</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATOR</t>
+          <t>PRESSURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -2452,13 +2440,13 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PI-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -2467,17 +2455,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>V-PAHH-213</t>
+          <t>V-TAHH-213</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>HIGH HIGH PRESSURE ALARM ASSOCIATED WITH PIT-213</t>
+          <t>TEMPERATURE ALARM HIGH HIGH ON A LINE</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE ALARM HIGH HIGH</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr"/>
@@ -2523,13 +2511,13 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -2538,20 +2526,24 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>V-TAHH-213</t>
+          <t>V-BV-2248</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>HIGH HIGH TEMPERATURE ALARM ASSOCIATED WITH TIT-213</t>
+          <t>BV,COMPRSR D/L VENT,K-V-201 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM HIGH HIGH</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>VALVE,BALL,1IN</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2594,35 +2586,39 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>V-TIT-213</t>
+          <t>V-BV-2248</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT ON LINE</t>
+          <t>BV,COMPRSR D/L VENT,K-V-201 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATING TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
+          <t>VALVE,BALL,1IN</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2665,13 +2661,13 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TIT-213 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -2680,20 +2676,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>V-PAHH-213</t>
+          <t>V-BV-2247</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE ALARM ON LINE</t>
+          <t>BV,COMPRSR DISCH LN,K-V-201 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE ALARM HIGH HIGH</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>VALVE,BALL,10IN</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10IN</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2736,35 +2736,39 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>V-TAHH-213</t>
+          <t>10IN-GV-V272-11502X</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM ON LINE</t>
+          <t>PIPING,FRM K-V-201 DISCH LN TO FLARE HDR</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM HIGH HIGH</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
+          <t>PIPING,10IN,DP:19.6 TO 15.8BARG,DT:-50 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>10IN</t>
+        </is>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2807,39 +2811,35 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TAHH-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2248</t>
+          <t>V-HS-214B</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BV,COMPRSR D/L VENT,K-V-201 TO FLARE HDR</t>
+          <t>RCI ALARM</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>VALVE,BALL,1IN</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1IN</t>
-        </is>
-      </c>
+          <t>HAND SWITCH</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -2882,13 +2882,13 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-HS-214B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -2897,22 +2897,22 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>V-BV-2247</t>
+          <t>V-RV-207</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>BV,COMPRSR DISCH LN,K-V-201 TO FLARE HDR</t>
+          <t>VALVE,TANK PRESSURE RELEIF,T-V-006</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>VALVE,BALL,10IN</t>
+          <t>VALVE,RELIEF,65BARG,1X2IN</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>10IN</t>
+          <t>65BARG,1X2IN</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2963,29 +2963,33 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>V-HS-214B</t>
+          <t>V-BV-2244</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>RCI ALARM</t>
+          <t>BV,RV D/S VENT,V-RV-207 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>HAND SWITCH</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
+          <t>VALVE,BALL,1IN</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -3028,39 +3032,35 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-HS-214B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>V-RV-207</t>
+          <t>TE-212</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>VALVE,TANK PRESSURE RELEIF,T-V-006</t>
+          <t>TEMPERATURE MEASUREMENT</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>VALVE,RELIEF,65BARG,1X2IN</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>65BARG,1X2IN</t>
-        </is>
-      </c>
+          <t>TEMPERATURE ELEMENT</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -3103,39 +3103,35 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: TE-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2244</t>
+          <t>V-TE-211</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>BV,RV D/S VENT,V-RV-207 TO FLARE HDR</t>
+          <t>TEM ELE,COMP SUCTION GAS TEMP,V-TIT-211</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>VALVE,BALL,1IN</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1IN</t>
-        </is>
-      </c>
+          <t>ELEMENT,TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -3178,32 +3174,32 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>V-TAHH-212</t>
+          <t>TW-212</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM ON LINE</t>
+          <t>TEMPERATURE MEASUREMENT</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM HIGH HIGH</t>
+          <t>THERMOWELL</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
@@ -3249,13 +3245,13 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TAHH-212 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: TW-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
@@ -3264,17 +3260,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>V-TIT-212</t>
+          <t>V-TW-211</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>TEMP TX 2,COMP SUCTION GAS TEMP,K-V-201</t>
+          <t>THERMOWELL,COMP SUC GAS TEMP,V-TIT-211</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TRANSMITTER,TEMPERATURE,INDICATING</t>
+          <t>THERMOWELL</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -3320,13 +3316,13 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -3335,17 +3331,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>V-TE-212</t>
+          <t>T-256</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>TEMP ELE,COMP SUCTION GAS TEMP,V-TIT-212</t>
+          <t>TEMPERATURE MEASUREMENT</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>ELEMENT,TEMPERATURE</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
@@ -3391,13 +3387,13 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-256 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3402,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TE-212</t>
+          <t>T-257</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3416,7 +3412,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE ELEMENT</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -3462,32 +3458,32 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: TE-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-257 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>TW-212</t>
+          <t>V-TI-211</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT</t>
+          <t>CONNECTED TO TIT-211</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>THERMOWELL</t>
+          <t>TEMPERATURE INDICATOR</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
@@ -3533,13 +3529,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: TW-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TI-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
@@ -3548,17 +3544,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>T-256</t>
+          <t>XV-203</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT</t>
+          <t>VALVE ACTUATOR BUBBLE</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -3604,13 +3600,13 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-256 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: XV-203 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -3619,17 +3615,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>V-TE-211</t>
+          <t>V-TIT-214</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>TEM ELE,COMP SUCTION GAS TEMP,V-TIT-211</t>
+          <t>TEMPERATURE INDICATING TRANSMITTER</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>ELEMENT,TEMPERATURE</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
@@ -3675,32 +3671,32 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TIT-214 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-02</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>V-TW-211</t>
+          <t>V-TAHH-214</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>THERMOWELL,COMP SUC GAS TEMP,V-TIT-211</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>THERMOWELL</t>
+          <t>SHARED DISPLAY/CONTROL</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -3746,32 +3742,32 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TAHH-214 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream | CONTROL_LOOP: CL-02</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>T-257</t>
+          <t>V-TAHH-214</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>TEMPERATURE ALARM HIGH HIGH</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
@@ -3817,32 +3813,32 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-257 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TAHH-214 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-02</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>V-TIT-211</t>
+          <t>V-TI-213</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>TEMP TX 1,COMP SUCTION GAS TEMP,K-V-201</t>
+          <t>TEMPERATURE INDICATOR</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>TRANSMITTER,TEMPERATURE,INDICATING</t>
+          <t>TEMPERATURE INDICATOR</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -3888,37 +3884,37 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TI-213 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>V-XV-203</t>
+          <t>V-BV-2246</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>ON/OFF VLV,B/W COMPRSR D/L &amp; S/L,K-V-201</t>
+          <t>BV,COMPRSR D/L VENT,K-V-201 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>VALVE,ON/OFF,3IN</t>
+          <t>VALVE,BALL,1IN</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>3IN</t>
+          <t>1IN</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3963,35 +3959,39 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>V-TIT-214</t>
+          <t>V-BV-2245</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT</t>
+          <t>BV,COMPRSR DISCH LN,K-V-201 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATING TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
+          <t>VALVE,BALL,6IN</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>6IN</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -4034,35 +4034,39 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TIT-214 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>V-TAHH-214</t>
+          <t>6IN-ETH-V058-61440X-PP</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM HIGH HIGH</t>
+          <t>PIPING,FRM K-V-201 DISCH LN TO V-RV-208</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>LOGIC BOX</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr"/>
+          <t>PIPING,6IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>6IN</t>
+        </is>
+      </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -4105,13 +4109,13 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TAHH-214 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | PARENT_EQUIP: 01/E-V-201A | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
@@ -4120,17 +4124,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>V-TAHH-214</t>
+          <t>V-ZX-209</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM HIGH HIGH</t>
+          <t>POSITION SWITCH, LIKELY PART OF A VALVE ASSEMBLY</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE ALARM HIGH HIGH</t>
+          <t>POSITION SWITCH</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -4176,13 +4180,13 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TAHH-214 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-ZX-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -4191,17 +4195,17 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>V-TI-213</t>
+          <t>V-ZLO-209</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR</t>
+          <t>POSITION SWITCH OPEN FOR VALVE</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR</t>
+          <t>POSITION SWITCH OPEN</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
@@ -4247,32 +4251,32 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TI-213 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-ZLO-209 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>V-TI-217</t>
+          <t>ZLC-209</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR</t>
+          <t>POSITION SWITCH CLOSED FOR VALVE</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR</t>
+          <t>POSITION SWITCH CLOSED</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -4318,13 +4322,13 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TI-217 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: ZLC-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -4333,22 +4337,22 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>V-BV-2246</t>
+          <t>V-BV-2243</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>BV,COMPRSR D/L VENT,K-V-201 TO FLARE HDR</t>
+          <t>BV,RELEIF VLV D/S,V-RV-207 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>VALVE,BALL,1IN</t>
+          <t>VALVE,BALL,2IN</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>1IN</t>
+          <t>2IN</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4393,13 +4397,13 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
@@ -4408,22 +4412,22 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2245</t>
+          <t>V-BV-2242</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>BV,COMPRSR DISCH LN,K-V-201 TO FLARE HDR</t>
+          <t>BV,RV U/S VENT,V-RV-207 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>VALVE,BALL,6IN</t>
+          <t>VALVE,BALL,1IN</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>6IN</t>
+          <t>1IN</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4468,13 +4472,13 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -4483,22 +4487,22 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>6IN-ETH-V058-61440X-PP</t>
+          <t>4IN-ETH-V060-61440X</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>PIPING,FRM K-V-201 DISCH LN TO V-RV-208</t>
+          <t>PIPING,FRM V-XV-203 TO K-V-201 INLET LN</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>PIPING,6IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+          <t>PIPING,4IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>6IN</t>
+          <t>4IN</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4543,32 +4547,32 @@
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>V-ZX-209</t>
+          <t>TI-211</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>POSITION SWITCH, LIKELY PART OF A VALVE ASSEMBLY</t>
+          <t>TEMPERATURE INDICATOR ON A LINE</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>POSITION SWITCH</t>
+          <t>TEMPERATURE INDICATOR</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -4614,35 +4618,39 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-ZX-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: TI-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>V-ZLO-209</t>
+          <t>V-XV-203</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH OPEN FOR VALVE</t>
+          <t>ON/OFF VLV,B/W COMPRSR D/L &amp; S/L,K-V-201</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH OPEN</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr"/>
+          <t>VALVE,ON/OFF,3IN</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>3IN</t>
+        </is>
+      </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -4685,13 +4693,13 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-ZLO-209 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
@@ -4700,17 +4708,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ZLC-209</t>
+          <t>V-FE</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>POSITION SWITCH CLOSED</t>
+          <t>FLOW ELEMENT ON A LINE</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>POSITION SWITCH CLOSED</t>
+          <t>FLOW ELEMENT</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -4756,35 +4764,39 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: ZLC-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-FE | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>V-RST-209</t>
+          <t>4IN-ETH-V060-61440X</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>RESET FUNCTION</t>
+          <t>PIPING,FRM V-XV-203 TO K-V-201 INLET LN</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr"/>
+          <t>PIPING,4IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>4IN</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -4827,39 +4839,35 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-RST-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2243</t>
+          <t>XY-203</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>BV,RELEIF VLV D/S,V-RV-207 TO FLARE HDR</t>
+          <t>CONTROLS ACTUATOR FOR XV-203</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>VALVE,BALL,2IN</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>2IN</t>
-        </is>
-      </c>
+          <t>SOLENOID VALVE</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -4902,13 +4910,13 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: XY-203 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -4917,17 +4925,17 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>V-TI-211</t>
+          <t>V-TIC-213</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR ON A LINE</t>
+          <t>INSTRUMENT BUBBLE WITH TAG V-TIC-213</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
@@ -4973,13 +4981,13 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TI-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TIC-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: upstream | CONTROL_LOOP: CL-02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
@@ -4988,7 +4996,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>TI-211</t>
+          <t>TI-213</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5044,35 +5052,39 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: TI-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: TI-213 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-02</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>XV-203</t>
+          <t>12IN-ETH-V012-61440X-PP</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>VALVE ON A LINE</t>
+          <t>PIPING,FRM K-V-201 D/L TO GAS COOLER</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>VALVE</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr"/>
+          <t>PIPING,12N,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>12IN</t>
+        </is>
+      </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5115,35 +5127,39 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: XV-203 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | PARENT_EQUIP: 01/E-V-201A | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>XY-203</t>
+          <t>2IN-ETH-V057-61440X</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>VALVE IN A SQUARE BOX</t>
+          <t>PIPING,FRM V-V-201 OUTLET LN TO V-RV-207</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>VALVE</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>PIPING,2IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2IN</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5186,13 +5202,13 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: XY-203 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -5201,20 +5217,24 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>V-TIC-213</t>
+          <t>V-BV-2242</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>BV,RV U/S VENT,V-RV-207 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr"/>
+          <t>VALVE,BALL,1IN</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5257,13 +5277,13 @@
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TIC-213 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
@@ -5272,20 +5292,24 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>V-TI-213</t>
+          <t>V-BV-2241</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR ON A LINE</t>
+          <t>BV,RELEIF VLV U/S,V-RV-207 TO FLARE HDR</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE INDICATOR</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
+          <t>VALVE,BALL,2IN</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2IN</t>
+        </is>
+      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5328,39 +5352,35 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-TI-213 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>12IN-ETH-V012-61440X-PP</t>
+          <t>V-FE-224</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>PIPING,FRM K-V-201 D/L TO GAS COOLER</t>
+          <t>FLOW ELEMENT,COMPRSR SUCTN LN,K-V-201</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>PIPING,12N,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>12IN</t>
-        </is>
-      </c>
+          <t>ELEMENT,FLOW</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5403,32 +5423,32 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>V-EZT-209</t>
+          <t>V-TT-217A</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CONNECTED TO A LOGIC BOX ABOVE</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -5474,35 +5494,39 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-EZT-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-TT-217A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>ZT-209</t>
+          <t>4IN-ETH-V059-61440X-PP</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>POSITION TRANSMITTER FOR VALVE</t>
+          <t>PIPING,FRM K-V-201 D/L TO V-XV-203 U/S</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>POSITION TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr"/>
+          <t>PIPING,4IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>4IN</t>
+        </is>
+      </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5545,39 +5569,35 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: ZT-209 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>2IN-ETH-V057-61440X</t>
+          <t>V-PIC-211</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>PIPING,FRM V-V-201 OUTLET LN TO V-RV-207</t>
+          <t>PRESSURE CONTROL LOOP</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>PIPING,2IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>2IN</t>
-        </is>
-      </c>
+          <t>PRESSURE INDICATING CONTROLLER</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5620,39 +5640,35 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>4IN-ETH-V059-61440X-PP</t>
+          <t>V-PI-212</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>PIPING,FRM K-V-201 D/L TO V-XV-203 U/S</t>
+          <t>PRESSURE INDICATOR CONNECTED TO A LINE, LIKELY MONITORING PRESSURE BEFORE A CONTROL VALVE.</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>PIPING,4IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>4IN</t>
-        </is>
-      </c>
+          <t>PRESSURE INDICATOR</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -5695,32 +5711,32 @@
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PI-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>V-PIC-210</t>
+          <t>PI-212</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE CONTROL LOOP</t>
+          <t>PRESSURE INDICATOR ON A LINE</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER</t>
+          <t>PRESSURE INDICATOR</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -5766,32 +5782,32 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-210 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PI-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-211</t>
+          <t>T-204A</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE CONTROL LOOP</t>
+          <t>TEMPERATURE TRANSMITTER ON A LINE</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr"/>
@@ -5837,13 +5853,13 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-204A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-02</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
@@ -5852,17 +5868,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>V-PI-212</t>
+          <t>S-HS-1466B</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATOR CONNECTED TO A LINE, LIKELY MONITORING PRESSURE BEFORE A CONTROL VALVE.</t>
+          <t>HAND SWITCH LOGIC/CONTROL FUNCTION</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATOR</t>
+          <t>SHARED DISPLAY/CONTROL</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -5908,13 +5924,13 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PI-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: S-HS-1466B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -5923,17 +5939,17 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>PI-212</t>
+          <t>T-255A</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATOR ON A LINE</t>
+          <t>TEMPERATURE TRANSMITTER CONNECTED TO PIPING</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATOR</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr"/>
@@ -5979,35 +5995,39 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PI-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-255A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>T-204A</t>
+          <t>V-BV-2249</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER ON A LINE</t>
+          <t>BV,FRM V-XV-202 TO KO DRUM I/L,V-V-201</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr"/>
+          <t>VALVE,BALL,2IN</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2IN</t>
+        </is>
+      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -6050,35 +6070,39 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-204A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>TT-204A</t>
+          <t>V-BV-2355</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT ON PIPING LINE</t>
+          <t>BV,KO DRUM INLET LINE DRAIN,V-V-201</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr"/>
+          <t>VALVE,BALL,1IN</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -6121,13 +6145,13 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: TT-204A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-03</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
@@ -6136,17 +6160,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>S-HS-1466B</t>
+          <t>T-201B</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>MANUAL SWITCH, POSSIBLY FOR A VALVE OR MOTOR</t>
+          <t>DIAMOND SYMBOL</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>HAND SWITCH</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -6192,13 +6216,13 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: HS-1466B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-201B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-03</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -6207,17 +6231,17 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>T-255A</t>
+          <t>T-217C</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER CONNECTED TO PIPING</t>
+          <t>TEMPERATURE INSTRUMENT</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
@@ -6263,39 +6287,35 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-255A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-217C | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>V-BV-2249</t>
+          <t>T-274B</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>BV,FRM V-XV-202 TO KO DRUM I/L,V-V-201</t>
+          <t>TEMPERATURE INSTRUMENT</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>VALVE,BALL,2IN</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2IN</t>
-        </is>
-      </c>
+          <t>INSTRUMENT BUBBLE</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -6338,13 +6358,13 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-274B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204 | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
@@ -6353,12 +6373,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>T-201A</t>
+          <t>T-217A</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>ON LINE C06B 61440</t>
+          <t>TEMPERATURE MEASUREMENT</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -6409,32 +6429,32 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-201A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-217A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>T-201B</t>
+          <t>V-FIC-207</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>DIAMOND SYMBOL</t>
+          <t>FLOW CONTROL LOOP</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>FLOW INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -6480,32 +6500,32 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-201B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-FIC-207 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>T-274B</t>
+          <t>V-PIC-210</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE T-274B</t>
+          <t>LOW SUCTION PRESSURE OVERRIDE</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr"/>
@@ -6551,32 +6571,32 @@
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-274B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-210 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>T-217A</t>
+          <t>V-PIC-210A</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT</t>
+          <t>INDIVIDUAL SUCTION PRESSURE CONTROL</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -6622,13 +6642,13 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-217A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-210A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
@@ -6637,17 +6657,17 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>V-FIC-207</t>
+          <t>V-PIC-212</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>FLOW CONTROL LOOP</t>
+          <t>PRESSURE INDICATING CONTROLLER WITH HIGH DISCHARGE PRESSURE OVERRIDE</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>FLOW INDICATING CONTROLLER</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr"/>
@@ -6693,13 +6713,13 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-FIC-207 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
@@ -6708,12 +6728,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>V-PIC-210A</t>
+          <t>S-PIC-146</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>INDIVIDUAL SUCTION PRESSURE CONTROL</t>
+          <t>PRESSURE INDICATING CONTROLLER WITH HIGH ARRIVAL PRESSURE OVERRIDE</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -6764,32 +6784,32 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-210A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: S-PIC-146 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-212</t>
+          <t>PT-212</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>HIGH DISCHARGE PRESSURE OVERRIDE</t>
+          <t>PRESSURE TRANSMITTER CONNECTED TO PIC-212</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER</t>
+          <t>PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr"/>
@@ -6835,13 +6855,13 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PT-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
@@ -6850,17 +6870,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>PT-212</t>
+          <t>PIC-1466B</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE TRANSMITTER FOR LOOP 212</t>
+          <t>PRESSURE INDICATING CONTROLLER, LIKELY PART OF A CONTROL LOOP, RECEIVING A SIGNAL FROM A LINE.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE TRANSMITTER</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -6906,13 +6926,13 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PT-212 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PIC-1466B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
@@ -6926,12 +6946,12 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH ON A SIGNAL LINE</t>
+          <t>UNCLASSIFIED SWITCH LOGIC/CONTROL FUNCTION</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH</t>
+          <t>SHARED DISPLAY/CONTROL</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr"/>
@@ -6983,7 +7003,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
@@ -6997,7 +7017,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>HAND SWITCH, LIKELY PART OF A CONTROL LOOP OR LOGIC SEQUENCE.</t>
+          <t>HAND SWITCH, LIKELY PART OF A CONTROL LOGIC SEQUENCE.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7054,7 +7074,7 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
@@ -7068,12 +7088,12 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH, LIKELY PART OF A CONTROL LOOP OR LOGIC SEQUENCE.</t>
+          <t>HAND SWITCH, LIKELY PART OF A CONTROL LOGIC SEQUENCE.</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH</t>
+          <t>HAND SWITCH</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr"/>
@@ -7119,13 +7139,13 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: XS-261 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: XS-261 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
@@ -7134,20 +7154,24 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>4-MGDV-6-50-2004-003</t>
+          <t>2IN-ETH-V067-61440X</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>PIPING,FRM V-XV-202 TO V-V-201 INLET LN</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
+          <t>PIPING,2IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2IN</t>
+        </is>
+      </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -7190,13 +7214,13 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '4-MGDV-6-50-2004-003' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | TAG_NORMALISED_FROM: 2IN-ETH-V067—61440X | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
@@ -7205,17 +7229,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>V-XV-202</t>
+          <t>PG-206</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>VALVE TAG</t>
+          <t>PRESSURE GAUGE</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>VALVE TAG</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr"/>
@@ -7261,39 +7285,35 @@
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-XV-202 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PG-206 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>2IN-ETH-V067-61440X</t>
+          <t>V-PG-206</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>PIPING,FRM V-XV-202 TO V-V-201 INLET LN</t>
+          <t>PRESSURE GAUGE CONNECTED TO A LINE WITH TWO GATE VALVES.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>PIPING,2IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2IN</t>
-        </is>
-      </c>
+          <t>PRESSURE GAUGE</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -7336,13 +7356,13 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | TAG_NORMALISED_FROM: 2IN-ETH-V067—61440X | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PG-206 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
@@ -7356,7 +7376,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE MEASUREMENT</t>
+          <t>CONNECTED TO PIPING</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -7407,13 +7427,13 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-274A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-274A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
@@ -7422,12 +7442,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>V-LIT-204</t>
+          <t>LIT-204</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LEVEL MEASUREMENT</t>
+          <t>CONNECTED TO PIPING</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7478,32 +7498,32 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-LIT-204 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: LIT-204 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>V-LIC-204</t>
+          <t>V-LIT-206</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>LEVEL CONTROL</t>
+          <t>CONNECTED TO PIPING</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>LEVEL INDICATING CONTROLLER</t>
+          <t>LEVEL INDICATING TRANSMITTER</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr"/>
@@ -7549,32 +7569,32 @@
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-LIC-204 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-LIT-206 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>V-LIT-206</t>
+          <t>S-V-204</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>LEVEL MEASUREMENT</t>
+          <t>STRAINER,KO DRUM OUTLET LINE,V-V-201</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>LEVEL INDICATING TRANSMITTER</t>
+          <t>STRAINER</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -7620,13 +7640,13 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-LIT-206 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
@@ -7697,7 +7717,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
@@ -7768,7 +7788,7 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
@@ -7782,7 +7802,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>HIGH SELECT RELAY FOR PRESSURE CONTROL</t>
+          <t>HIGH SELECT RELAY RECEIVING INPUTS FROM LOW SUCTION PRESSURE OVERRIDE AND INDIVIDUAL SUCTION PRESSURE CONTROL.</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -7839,7 +7859,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
@@ -7904,13 +7924,13 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-Y2-207' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-Y2-207' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
@@ -7924,7 +7944,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>LOGIC BLOCK</t>
+          <t>CONNECTED TO V-Y2-207</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -7975,13 +7995,13 @@
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-XS-270 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-XS-270 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-07</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
@@ -7995,7 +8015,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>LOGIC BLOCK</t>
+          <t>CONNECTED TO V-Y2-207</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -8052,7 +8072,7 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
@@ -8066,12 +8086,12 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>SPEED CONTROLLER CONNECTED TO A CONTROL LOOP.</t>
+          <t>CONNECTED TO A SIGNAL LINE, LIKELY PART OF A CONTROL LOOP.</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>SPEED CONTROLLER</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr"/>
@@ -8117,32 +8137,32 @@
       </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-SC-201 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-SC-201 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-07</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>V-LY-206</t>
+          <t>V-XI-220</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>LEVEL CONTROL LOGIC</t>
+          <t>INSTRUMENT BUBBLE WITH TAG V-XI-220</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>LEVEL RELAY</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -8188,32 +8208,32 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-LY-206 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-XI-220 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>V-XI-220</t>
+          <t>Y2-207</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE WITH TAG V-XI-220</t>
+          <t>LOGIC CONTROLLER RECEIVING MULTIPLE INPUTS AND SENDING OUTPUTS</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>LOGIC CONTROLLER</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr"/>
@@ -8259,32 +8279,32 @@
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-XI-220 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: Y2-207 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Y2-207</t>
+          <t>V-PIC-252A</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>LOGIC CONTROLLER RECEIVING MULTIPLE INPUTS</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>LOGIC CONTROLLER</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -8330,13 +8350,13 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: Y2-207 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-252A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
@@ -8345,12 +8365,12 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>V-PIC-252A</t>
+          <t>V-PIC-252B</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER CONNECTED TO A SIGNAL LINE.</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -8401,13 +8421,13 @@
       </c>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-252A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-252B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
@@ -8416,17 +8436,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>V-PIC-252B</t>
+          <t>V-Y-252</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER CONNECTED TO A SIGNAL LINE.</t>
+          <t>LOGIC CONTROLLER</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER</t>
+          <t>LOGIC CONTROLLER</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -8472,13 +8492,13 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-252B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-Y-252 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
@@ -8549,7 +8569,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
@@ -8620,7 +8640,7 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
@@ -8639,7 +8659,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr"/>
@@ -8691,7 +8711,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
@@ -8762,26 +8782,26 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>V-GV-920</t>
+          <t>T-246A</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>ON 1" LINE</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
@@ -8827,35 +8847,39 @@
       </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-GV-920 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-246A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>T-246A</t>
+          <t>V-GV-922</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>GV,LEVEL CONTROL VALVE D/S LINE,V-LV-206</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
+          <t>VALVE,GATE,1IN</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -8898,13 +8922,13 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-246A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
@@ -8913,24 +8937,20 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>V-GV-922</t>
+          <t>V-FZ-208</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>GV,LEVEL CONTROL VALVE D/S LINE,V-LV-206</t>
+          <t>FLOW LOGIC/SWITCH</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>VALVE,GATE,1IN</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>1IN</t>
-        </is>
-      </c>
+          <t>LOGIC BOX</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr"/>
       <c r="G117" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -8973,32 +8993,32 @@
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-FZ-208 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>V-FZ-208</t>
+          <t>V-FZT-208</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>FLOW SWITCH OR LOGIC ELEMENT</t>
+          <t>POSITION TRANSMITTER F/ V-FCV-208</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BOX</t>
+          <t>TRANSMITTER,POSITION</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -9044,13 +9064,13 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-FZ-208 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
@@ -9059,17 +9079,17 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>V-FZT-208</t>
+          <t>V-FY-208</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>POSITION TRANSMITTER F/ V-FCV-208</t>
+          <t>SOLENOID VALVE,V-FCV-208</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>TRANSMITTER,POSITION</t>
+          <t>VALVE,SOLENOID</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr"/>
@@ -9115,32 +9135,32 @@
       </c>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>V-FY-208</t>
+          <t>V-PIC-004A</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>SOLENOID VALVE,V-FCV-208</t>
+          <t>PRESSURE CONTROL LOOP</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>VALVE,SOLENOID</t>
+          <t>PRESSURE INDICATING CONTROLLER</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
@@ -9186,27 +9206,27 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-PIC-004A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>V-252A</t>
+          <t>PIC-04A</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE WITH TAG V-252A</t>
+          <t>CONNECTED TO A LOGIC LINE</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -9257,13 +9277,13 @@
       </c>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-252A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: PIC-04A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
@@ -9272,20 +9292,24 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>V-PIC-004A</t>
+          <t>V-GV-922</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE WITH TAG V-PIC-004A</t>
+          <t>GV,LEVEL CONTROL VALVE D/S LINE,V-LV-206</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr"/>
+          <t>VALVE,GATE,1IN</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>1IN</t>
+        </is>
+      </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -9328,13 +9352,13 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-PIC-004A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
@@ -9343,17 +9367,17 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>PIC-04A</t>
+          <t>T-246B</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>CONNECTED TO A SIGNAL LINE</t>
+          <t>CONNECTED TO HORIZONTAL LINE</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING CONTROLLER</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr"/>
@@ -9399,32 +9423,32 @@
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PIC-04A | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-246B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>1IN-D-V006-C06B</t>
+          <t>T-246C</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>HORIZONTAL LINE</t>
+          <t>CONNECTED TO HORIZONTAL LINE</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -9470,13 +9494,13 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '1IN-D-V006-C06B' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-246C | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
@@ -9485,12 +9509,12 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>V-GV-922</t>
+          <t>V-GV-923</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>GV,LEVEL CONTROL VALVE D/S LINE,V-LV-206</t>
+          <t>GV,KO DRUM DRAIN LINE,V-V-201</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -9551,7 +9575,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
@@ -9622,7 +9646,7 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
@@ -9631,17 +9655,17 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>V-ZLC-208</t>
+          <t>V-FZSC-208</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>POSITION SWITCH, CLOSED</t>
+          <t>LIMIT SWITCH CLOSE,V-FCV-208</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>SWITCH,LIMIT,CLOSE</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr"/>
@@ -9687,32 +9711,32 @@
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-ZLC-208 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>V-ZLO-208</t>
+          <t>V-FZSO-208</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>POSITION SWITCH, OPEN</t>
+          <t>LIMIT SWITCH OPEN,V-FCV-208</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>SWITCH,LIMIT,OPEN</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
@@ -9758,13 +9782,13 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-ZLO-208 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
@@ -9773,17 +9797,17 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>V-FZSC-208</t>
+          <t>V-FZY-208</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>LIMIT SWITCH CLOSE,V-FCV-208</t>
+          <t>I/P CONVERTER FOR V-FV-208</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>SWITCH,LIMIT,CLOSE</t>
+          <t>I/P CONVERTOR</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr"/>
@@ -9829,13 +9853,13 @@
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
@@ -9844,17 +9868,17 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>V-FZSO-208</t>
+          <t>V-ZY-208</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>LIMIT SWITCH OPEN,V-FCV-208</t>
+          <t>CONTROL VALVE WITH POSITIONER</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>SWITCH,LIMIT,OPEN</t>
+          <t>CONTROL VALVE</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
@@ -9900,35 +9924,39 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-ZY-208 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>V-FZY-208</t>
+          <t>10IN-ETH-V061-61440X</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>I/P CONVERTER FOR V-FV-208</t>
+          <t>PIPING,FRM V-FV-208 D/S TO V-V-201 I/L</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>I/P CONVERTOR</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr"/>
+          <t>PIPING,10IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>10IN</t>
+        </is>
+      </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -9971,32 +9999,32 @@
       </c>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>V-ZY-208</t>
+          <t>8IN-ETH-V066-61440X</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>CONTROL VALVE WITH POSITIONER</t>
+          <t>PIPING LINE SEGMENT</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>CONTROL VALVE</t>
+          <t>PIPING LINE</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -10042,13 +10070,13 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-ZY-208 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: 8IN-ETH-V066-61440X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
@@ -10057,24 +10085,20 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>10IN-ETH-V061-61440X</t>
+          <t>2IN-ETH-V018</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>PIPING,FRM V-FV-208 D/S TO V-V-201 I/L</t>
+          <t>PIPING LINE DESIGNATION</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>PIPING,10IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>10IN</t>
-        </is>
-      </c>
+          <t>PIPING LINE NUMBER</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -10117,37 +10141,37 @@
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '2IN-ETH-V018' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>V-GV-923</t>
+          <t>V-FV-208</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>GV,KO DRUM DRAIN LINE,V-V-201</t>
+          <t>FLOW CV,COMP ANTI SURGE VALVE,K-V-201</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>VALVE,GATE,1IN</t>
+          <t>VALVE,CONTROL,FLOW,6IN</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>1IN</t>
+          <t>6IN</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -10196,667 +10220,8 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>148</v>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUMENTATION</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>T-246B</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUMENT CONNECTED TO PIPING</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUMENT BUBBLE</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr"/>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M135" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N135" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O135" s="3" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: T-246B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>INSTRUMENTATION</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>T-246C</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>INSTRUMENT CONNECTED TO PIPING</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>INSTRUMENT BUBBLE</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N136" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O136" s="2" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: T-246C | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>PIPING</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>8IN-ETH-V066-61440X</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>PIPING LINE</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>PIPING LINE NUMBER</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr"/>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M137" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N137" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O137" s="3" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: 8IN-ETH-V066-61440X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-2242</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>BV,RV U/S VENT,V-RV-207 TO FLARE HDR</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>VALVE,BALL,1IN</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>1IN</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M138" s="2" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N138" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>PIPING</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>4IN-ETH-V060-61440X</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>PIPING,FRM V-XV-203 TO K-V-201 INLET LN</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>PIPING,4IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>4IN</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M139" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N139" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O139" s="3" t="inlineStr">
-        <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>V-BV-2242</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>BV,RV U/S VENT,V-RV-207 TO FLARE HDR</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>VALVE,BALL,1IN</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>1IN</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M140" s="2" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N140" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>V-BV-2241</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>BV,RELEIF VLV U/S,V-RV-207 TO FLARE HDR</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>VALVE,BALL,2IN</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>2IN</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M141" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N141" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O141" s="3" t="inlineStr">
-        <is>
-          <t>WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>PIPING</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>4IN-ETH-V060-61440X</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>PIPING,FRM V-XV-203 TO K-V-201 INLET LN</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>PIPING,4IN,DP:102.1 TO 90.2BARG,DT:0 TO 150DEG C</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>4IN</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M142" s="2" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N142" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>S-V-204</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>STRAINER,KO DRUM OUTLET LINE,V-V-201</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>STRAINER</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr"/>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K143" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M143" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N143" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O143" s="3" t="inlineStr">
-        <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O143"/>
+  <autoFilter ref="A1:O134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10868,7 +10233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10985,26 +10350,26 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>01-E-V-201A</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>GAS COOLER</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>LOGIC DIAMOND</t>
+          <t>GAS COOLER</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -11050,11 +10415,11 @@
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '004' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '01/E-V-201A' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 01/E-V-201A | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P2" s="6" t="n">
-        <v>0.773</v>
+        <v>0.743</v>
       </c>
       <c r="Q2" s="7" t="inlineStr">
         <is>
@@ -11069,26 +10434,26 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>004X</t>
+          <t>10IN</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>PIPING LINE SIZE</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>LOGIC DIAMOND</t>
+          <t>PIPING LINE NUMBER</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -11134,7 +10499,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '004X' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '10IN' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P3" s="8" t="n">
@@ -11153,26 +10518,26 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>12-ETH-VO06-C03B</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>PIPING LINE NUMBER</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>LOGIC DIAMOND</t>
+          <t>PIPING LINE NUMBER</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
@@ -11218,11 +10583,11 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '009' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '12°-ETH-VO06-C03B' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 12°-ETH-VO06-C03B | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.773</v>
+        <v>0.695</v>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
@@ -11237,26 +10602,26 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>009X</t>
+          <t>12IN-NOTE-21</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>MAIN HORIZONTAL LINE</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LOGIC DIAMOND</t>
+          <t>PIPING LINE NUMBER</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
@@ -11302,11 +10667,11 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '009X' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '12IN-NOTE 21' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 12IN-NOTE 21 | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.773</v>
+        <v>0.745</v>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
@@ -11321,26 +10686,26 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>01-E-V-201A</t>
+          <t>1IN</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>GAS COOLERS</t>
+          <t>ON BRANCH LINE</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>EQUIPMENT TAG</t>
+          <t>SPECTACLE BLIND</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
@@ -11386,11 +10751,11 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '01/E-V-201A' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 01/E-V-201A | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '1IN' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.743</v>
+        <v>0.768</v>
       </c>
       <c r="Q6" s="7" t="inlineStr">
         <is>
@@ -11405,7 +10770,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>194</v>
+        <v>110</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -11414,12 +10779,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1-D-V00</t>
+          <t>1IN</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>PIPING LINE EXITING BOTTOM RIGHT</t>
+          <t>BRANCH LINE SIZE</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -11470,11 +10835,11 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '1°-D-V00' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 1°-D-V00 | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '1IN' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.638</v>
+        <v>0.716</v>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
@@ -11489,26 +10854,26 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>12-ETH-VO06-C03B</t>
+          <t>201A</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>LOGIC FUNCTION OR INTERLOCK.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>LOGIC DIAMOND</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -11554,11 +10919,11 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '12°-ETH-VO06-C03B' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 12°-ETH-VO06-C03B | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '201A' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.695</v>
+        <v>0.773</v>
       </c>
       <c r="Q8" s="7" t="inlineStr">
         <is>
@@ -11573,26 +10938,26 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>193</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>12IN-NOTE-21</t>
+          <t>212</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>MAIN HORIZONTAL LINE</t>
+          <t>INSTRUMENT BUBBLE WITH NUMBER 212</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -11638,11 +11003,11 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '12IN-NOTE 21' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 12IN-NOTE 21 | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '212' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201 | CONTROL_LOOP: CL-06</t>
         </is>
       </c>
       <c r="P9" s="8" t="n">
-        <v>0.745</v>
+        <v>0.773</v>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
@@ -11657,26 +11022,26 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>1IN</t>
+          <t>213</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ON BRANCH LINE</t>
+          <t>INSTRUMENT BUBBLE, TOP PART CUT OFF</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>SPECTACLE BLIND</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -11722,11 +11087,11 @@
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '1IN' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '213' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.74</v>
+        <v>0.716</v>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
@@ -11741,26 +11106,26 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>197</v>
+        <v>102</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>1IN</t>
+          <t>2INCSO</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>BRANCH LINE SIZE</t>
+          <t>ON 2" LINE</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr"/>
@@ -11806,11 +11171,11 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '1IN' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '2IN,CSO' | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 2IN,CSO | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P11" s="8" t="n">
-        <v>0.716</v>
+        <v>0.771</v>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
@@ -11825,26 +11190,26 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>201A</t>
+          <t>4INX3IN-ETH-V060-61440X-PP</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION OR INTERLOCK.</t>
+          <t>PIPING LINE</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>LOGIC DIAMOND</t>
+          <t>PIPING LINE NUMBER</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -11890,7 +11255,7 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '201A' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '4INX3IN-ETH-V060-61440X-PP' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
       <c r="P12" s="6" t="n">
@@ -11909,26 +11274,26 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>SB-6IN</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE WITH TAG 212</t>
+          <t>ON LINE CONNECTING TO COMPRESSOR</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>RESTRICTION ORIFICE</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
@@ -11974,11 +11339,11 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '212' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'SB 6IN' | NOT_IN_REGISTER | TAG_NORMALISED_FROM: SB 6IN | WITHIN_REVISION_CLOUD | PARENT_EQUIP: K-V-201</t>
         </is>
       </c>
       <c r="P13" s="8" t="n">
-        <v>0.773</v>
+        <v>0.759</v>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
@@ -11993,26 +11358,26 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>V-GV-XX</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE, TOP PART CUT OFF</t>
+          <t>ISOLATION VALVE</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -12058,11 +11423,11 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '213' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX...' | NOT_IN_REGISTER | TAG_NORMALISED_FROM: V-GV-XX... | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.716</v>
+        <v>0.715</v>
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
@@ -12077,7 +11442,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -12086,17 +11451,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2INCSO</t>
+          <t>V-GV-XX001</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ON 2" LINE</t>
+          <t>CONNECTED TO PIPING</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr"/>
@@ -12142,11 +11507,11 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '2IN,CSO' | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 2IN,CSO | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX001' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P15" s="8" t="n">
-        <v>0.762</v>
+        <v>0.795</v>
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
@@ -12161,7 +11526,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -12170,17 +11535,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>3INFORB</t>
+          <t>V-GV-XX002</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>VALVE ON PIPING LINE</t>
+          <t>CONNECTED TO PIPING</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -12226,11 +11591,11 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: '3IN,FO,RB' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: 3IN,FO,RB | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX002' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.756</v>
+        <v>0.768</v>
       </c>
       <c r="Q16" s="7" t="inlineStr">
         <is>
@@ -12245,26 +11610,26 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SB-6IN</t>
+          <t>V-GV-XX003</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ON LINE CONNECTING TO COMPRESSOR</t>
+          <t>ISOLATION VALVE</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>RESTRICTION ORIFICE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
@@ -12310,11 +11675,11 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'SB 6IN' | NOT_IN_REGISTER | TAG_NORMALISED_FROM: SB 6IN | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX003' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P17" s="8" t="n">
-        <v>0.759</v>
+        <v>0.794</v>
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
@@ -12329,26 +11694,26 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>V-GV-XX004</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>ON LINE C06B 61440X</t>
+          <t>ISOLATION VALVE</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -12394,11 +11759,11 @@
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'T-...' | Transmitter tag missing T/IT: T-... | NOT_IN_REGISTER | TAG_NORMALISED_FROM: T-... | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX004' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.773</v>
+        <v>0.796</v>
       </c>
       <c r="Q18" s="7" t="inlineStr">
         <is>
@@ -12413,7 +11778,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -12422,17 +11787,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>T-217B</t>
+          <t>V-TIT</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER ON A LINE</t>
+          <t>BOTTOM RIGHT, PARTIALLY VISIBLE</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE TRANSMITTER</t>
+          <t>TEMPERATURE INDICATING TRANSMITTER</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
@@ -12478,7 +11843,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: T-217B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>VALIDATION_FAIL: Transmitter tag missing T/IT: V-TIT | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P19" s="8" t="n">
@@ -12497,7 +11862,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -12506,20 +11871,24 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>K-V-201</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>VALVE ON PIPING LINE</t>
+          <t>ETHANE GAS COMPRESSOR # 2,STATION-V</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr"/>
+          <t>COMPRESSOR,GAS,ETHANE,1900TPD</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>1900TPD,10662RPM</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -12562,26 +11931,26 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'UNKNOWN' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | WITHIN_REVISION_CLOUD | FLOW: upstream</t>
         </is>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.793</v>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>MISSING_TAG: no OCR text extracted</t>
+          <t>LOW_TEXT_CONF: c_text=0.41 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -12590,17 +11959,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>V-GV-XX</t>
+          <t>V-915</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ISOLATION VALVE</t>
+          <t>ON LINE CONNECTED TO PIT-210</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
@@ -12646,26 +12015,26 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX...' | NOT_IN_REGISTER | TAG_NORMALISED_FROM: V-GV-XX... | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-915 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-06</t>
         </is>
       </c>
       <c r="P21" s="8" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="Q21" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.659</v>
+      </c>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>LOW_TEXT_CONF: c_text=0.72 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -12674,17 +12043,17 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>V-GV-XX001</t>
+          <t>V-BV-22</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>VALVE ON VERTICAL LINE, MARKED WITH REVISION CLOUD</t>
+          <t>ON 10" LINE</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -12730,26 +12099,26 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX001' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-BV-22 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.799</v>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.726</v>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>LOW_TEXT_CONF: c_text=0.68 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -12758,12 +12127,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>V-GV-XX001</t>
+          <t>V-GV-904</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>ISOLATION VALVE</t>
+          <t>LOCKED OPEN GATE VALVE ON A 2" 600# LINE</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -12814,26 +12183,26 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX001' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-904 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P23" s="8" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="Q23" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.701</v>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>LOW_TEXT_CONF: c_text=0.52 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -12842,12 +12211,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>V-GV-XX002</t>
+          <t>V-GV-917</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>ISOLATION VALVE</t>
+          <t>ON 1 1/2" LINE</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12898,26 +12267,26 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX002' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-917 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: 01/E-V-201A</t>
         </is>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.697</v>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>LOW_TEXT_CONF: c_text=0.53 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -12926,20 +12295,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>V-GV-XX003</t>
+          <t>V-NRV-748</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>ISOLATION VALVE</t>
+          <t>NRV,KO DRUM INLET LINE,V-V-201</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
+          <t>VALVE,CHECK,12IN</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>12IN</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -12982,45 +12355,45 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX003' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>NO_SCOPE_DEFINITION_FOUND | TAG_NORMALISED_FROM: V—NRV-748 | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P25" s="8" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.796</v>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>LOW_TEXT_CONF: c_text=0.42 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>V-GV-XX004</t>
+          <t>V-XV-202</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>ISOLATION VALVE</t>
+          <t>VALVE TAG</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
+          <t>VALVE</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
@@ -13066,45 +12439,45 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-GV-XX004' | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-XV-202 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>P1</t>
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>LOW_TEXT_CONF: c_text=0.48 (threshold 0.75)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>PIPING</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>V-NRV</t>
+          <t>4IN-ETH-V061-61440X-PP</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>ON 12" LINE</t>
+          <t>PIPING LINE</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>CHECK VALVE</t>
+          <t>PIPING LINE NUMBER</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr"/>
@@ -13150,26 +12523,26 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: Does not match ISA-5.1 format: 'V-NRV-...' | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | TAG_NORMALISED_FROM: V-NRV-... | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: 4IN-ETH-V061-61440X-PP | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P27" s="8" t="n">
         <v>0.773</v>
       </c>
-      <c r="Q27" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="Q27" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>VALIDATION_FAIL: FAIL</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -13178,12 +12551,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>12IN-ETH-V009-C06B</t>
+          <t>C06B-61440X</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER 12"-ETH-V009-C06</t>
+          <t>PIPING LINE</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13234,45 +12607,45 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: 12IN-ETH-V009-C06B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: C06B-61440X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: 01/E-V-201A | FLOW: downstream</t>
         </is>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="Q28" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+        <v>0.773</v>
+      </c>
+      <c r="Q28" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>LOW_TEXT_CONF: c_text=0.58 (threshold 0.75)</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>195</v>
+        <v>43</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>V-915</t>
+          <t>I-004X</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ON LINE CONNECTED TO PIT-210</t>
+          <t>LOGIC DIAMOND WITH 'I' OVER '004X', CONNECTED TO OTHER LOGIC ELEMENTS.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>VALVE</t>
+          <t>LOGIC DIAMOND</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
@@ -13318,45 +12691,45 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-915 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: I-004X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
       <c r="P29" s="8" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="Q29" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+        <v>0.773</v>
+      </c>
+      <c r="Q29" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>LOW_TEXT_CONF: c_text=0.72 (threshold 0.75)</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>V-BV-22</t>
+          <t>I-009X</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>VALVE ON 10" LINE</t>
+          <t>LOGIC DIAMOND WITH 'I' OVER '009X', CONNECTED TO OTHER LOGIC ELEMENTS.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>LOGIC DIAMOND</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
@@ -13402,26 +12775,26 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-BV-22 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: I-009X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="Q30" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+        <v>0.773</v>
+      </c>
+      <c r="Q30" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>LOW_TEXT_CONF: c_text=0.59 (threshold 0.75)</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -13430,17 +12803,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>V-GV-904</t>
+          <t>S-Y1</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>ON A 2" 600# LINE</t>
+          <t>HIGH SELECT LOGIC BLOCK</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>GATE VALVE (LOCKED OPEN)</t>
+          <t>HIGH SELECT RELAY</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr"/>
@@ -13486,45 +12859,45 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-GV-904 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: S-Y1 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P31" s="8" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="Q31" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+        <v>0.773</v>
+      </c>
+      <c r="Q31" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>LOW_TEXT_CONF: c_text=0.52 (threshold 0.75)</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>V-GV-917</t>
+          <t>T-201A</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>ON 1 1/2" LINE</t>
+          <t>DIAMOND SYMBOL, LIKELY A LOGIC OR INTERLOCK REFERENCE</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>GATE VALVE</t>
+          <t>INSTRUMENT BUBBLE</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
@@ -13570,52 +12943,48 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-GV-917 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-201A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="Q32" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+        <v>0.773</v>
+      </c>
+      <c r="Q32" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>LOW_TEXT_CONF: c_text=0.53 (threshold 0.75)</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>MECHANICAL</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>V-NRV-748</t>
+          <t>T-201C</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>NRV,KO DRUM INLET LINE,V-V-201</t>
+          <t>LOGIC FUNCTION OR INTERLOCK.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>VALVE,CHECK,12IN</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>12IN</t>
-        </is>
-      </c>
+          <t>LOGIC DIAMOND</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
           <t>4224-MGDV-6-50-2004</t>
@@ -13658,45 +13027,45 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>NO_SCOPE_DEFINITION_FOUND | TAG_NORMALISED_FROM: V—NRV-748 | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-201C | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-03</t>
         </is>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="Q33" s="11" t="inlineStr">
-        <is>
-          <t>P2</t>
+        <v>0.773</v>
+      </c>
+      <c r="Q33" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>LOW_TEXT_CONF: c_text=0.42 (threshold 0.75)</t>
+          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>4IN-ETH-V061-61440X-PP</t>
+          <t>T-217B</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE</t>
+          <t>CONNECTED TO PIPING LINE</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>TEMPERATURE ELEMENT</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
@@ -13742,13 +13111,13 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: 4IN-ETH-V061-61440X-PP | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-217B | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
       <c r="P34" s="6" t="n">
         <v>0.773</v>
       </c>
-      <c r="Q34" s="12" t="inlineStr">
+      <c r="Q34" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -13761,26 +13130,26 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>4INX3IN-ETH-V060-61440X-PP</t>
+          <t>T-46A</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>PIPING LINE SPECIFICATION</t>
+          <t>LOGIC OR INTERLOCK FUNCTION</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>PIPING LINE</t>
+          <t>INSTRUMENT DIAMOND</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
@@ -13826,13 +13195,13 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: 61440X-PP | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: T-46A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P35" s="8" t="n">
         <v>0.773</v>
       </c>
-      <c r="Q35" s="13" t="inlineStr">
+      <c r="Q35" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -13845,26 +13214,26 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>PIPING</t>
+          <t>INSTRUMENTATION</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>C06B-61440X</t>
+          <t>TE-211</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE</t>
+          <t>CONNECTED TO HORIZONTAL LINE</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>PIPING LINE NUMBER</t>
+          <t>TEMPERATURE ELEMENT</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
@@ -13910,13 +13279,13 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: C06B-61440X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: TE-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
       <c r="P36" s="6" t="n">
         <v>0.773</v>
       </c>
-      <c r="Q36" s="12" t="inlineStr">
+      <c r="Q36" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -13929,26 +13298,26 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>I-004X</t>
+          <t>V-201</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>LOGIC BOX</t>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
@@ -13994,13 +13363,13 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: I-004X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-201 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: KM-V-201 | FLOW: downstream</t>
         </is>
       </c>
       <c r="P37" s="8" t="n">
         <v>0.773</v>
       </c>
-      <c r="Q37" s="13" t="inlineStr">
+      <c r="Q37" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14013,26 +13382,26 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>I-009X</t>
+          <t>V-BV-1920</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION</t>
+          <t>ON A 2" LINE, NEAR A LEVEL CONTROLLER.</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>LOGIC BOX</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
@@ -14078,13 +13447,13 @@
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: I-009X | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-BV-1920 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q38" s="12" t="inlineStr">
+        <v>0.764</v>
+      </c>
+      <c r="Q38" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14097,26 +13466,26 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>PIT-212</t>
+          <t>V-BV-76</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>PRESSURE INDICATING TRANSMITTER</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
@@ -14162,13 +13531,13 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: PIT-212 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-BV-76 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q39" s="13" t="inlineStr">
+        <v>0.758</v>
+      </c>
+      <c r="Q39" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14181,26 +13550,26 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>T-201C</t>
+          <t>V-BV-760</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>LOGIC FUNCTION OR INTERLOCK.</t>
+          <t>ON 12" LINE</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>LOGIC DIAMOND</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
@@ -14246,13 +13615,13 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-201C | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-BV-760 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream | CONTROL_LOOP: CL-00</t>
         </is>
       </c>
       <c r="P40" s="6" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q40" s="12" t="inlineStr">
+        <v>0.79</v>
+      </c>
+      <c r="Q40" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14265,26 +13634,26 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>T-255B</t>
+          <t>V-BV-761</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT TAG</t>
+          <t>ON A 2" LINE, NEAR A LEVEL CONTROLLER.</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENT BUBBLE</t>
+          <t>BALL VALVE</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
@@ -14330,13 +13699,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-255B | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-BV-761 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-03</t>
         </is>
       </c>
       <c r="P41" s="8" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q41" s="13" t="inlineStr">
+        <v>0.758</v>
+      </c>
+      <c r="Q41" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14349,26 +13718,26 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>T-46A</t>
+          <t>V-GLV-523</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>LOGIC OR INTERLOCK FUNCTION</t>
+          <t>VALVE ON A LINE</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENT DIAMOND</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
@@ -14414,13 +13783,13 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: T-46A | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GLV-523 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-05</t>
         </is>
       </c>
       <c r="P42" s="6" t="n">
         <v>0.773</v>
       </c>
-      <c r="Q42" s="12" t="inlineStr">
+      <c r="Q42" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14433,26 +13802,26 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>TE-211</t>
+          <t>V-GV-903</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CONNECTED TO TIT-211</t>
+          <t>ISOLATION VALVE</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>TEMPERATURE ELEMENT</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
@@ -14498,13 +13867,13 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: TE-211 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-903 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P43" s="8" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q43" s="13" t="inlineStr">
+        <v>0.792</v>
+      </c>
+      <c r="Q43" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14517,7 +13886,7 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -14526,17 +13895,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>V-201</t>
+          <t>V-GV-907</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>MOTOR</t>
+          <t>CONNECTED TO A VESSEL</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>MOTOR</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
@@ -14582,13 +13951,13 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-201 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-907 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q44" s="12" t="inlineStr">
+        <v>0.762</v>
+      </c>
+      <c r="Q44" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14601,7 +13970,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -14610,17 +13979,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>V-BV-1918</t>
+          <t>V-GV-908</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>ON 2" LINE</t>
+          <t>CONNECTED TO A VESSEL</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
@@ -14666,13 +14035,13 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-BV-1918 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-908 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P45" s="8" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="Q45" s="13" t="inlineStr">
+        <v>0.763</v>
+      </c>
+      <c r="Q45" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14685,7 +14054,7 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -14694,17 +14063,17 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>V-BV-1920</t>
+          <t>V-GV-91</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>ON 2" LINE</t>
+          <t>ON A HORIZONTAL PIPING LINE</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
@@ -14750,13 +14119,13 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-BV-1920 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-91 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | CONTROL_LOOP: CL-04</t>
         </is>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="Q46" s="12" t="inlineStr">
+        <v>0.765</v>
+      </c>
+      <c r="Q46" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14769,7 +14138,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -14778,17 +14147,17 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>V-BV-76</t>
+          <t>V-GV-911</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>VALVE ON LINE</t>
+          <t>ON PIPING LINE</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
@@ -14834,13 +14203,13 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-BV-76 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-911 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | PARENT_EQUIP: S-V-204</t>
         </is>
       </c>
       <c r="P47" s="8" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="Q47" s="13" t="inlineStr">
+        <v>0.772</v>
+      </c>
+      <c r="Q47" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14853,7 +14222,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -14862,17 +14231,17 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>V-BV-760</t>
+          <t>V-GV-914</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>ON 12" LINE</t>
+          <t>ON VERTICAL LINE</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
@@ -14918,13 +14287,13 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-BV-760 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-914 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P48" s="6" t="n">
         <v>0.79</v>
       </c>
-      <c r="Q48" s="12" t="inlineStr">
+      <c r="Q48" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -14937,7 +14306,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -14946,17 +14315,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>V-BV-761</t>
+          <t>V-GV-915</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ON 2" LINE</t>
+          <t>VALVE ON LINE</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>BALL VALVE</t>
+          <t>GATE VALVE</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
@@ -15002,13 +14371,13 @@
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-BV-761 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-GV-915 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
         </is>
       </c>
       <c r="P49" s="8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Q49" s="13" t="inlineStr">
+        <v>0.785</v>
+      </c>
+      <c r="Q49" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15021,26 +14390,26 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>INSTRUMENTATION</t>
+          <t>MECHANICAL</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>V-FE</t>
+          <t>V-NRV</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>FLOW ELEMENT ON A LINE</t>
+          <t>ON THE MAIN 12" LINE.</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>FLOW ELEMENT</t>
+          <t>CHECK VALVE</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
@@ -15086,13 +14455,13 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-FE | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-NRV | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="Q50" s="12" t="inlineStr">
+        <v>0.77</v>
+      </c>
+      <c r="Q50" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15105,7 +14474,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -15114,17 +14483,17 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>V-GLV-523</t>
+          <t>V-NRV-1918</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>ON HORIZONTAL LINE</t>
+          <t>ON 12" LINE</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>GLOBE VALVE</t>
+          <t>CHECK VALVE</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
@@ -15170,13 +14539,13 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>WARN: Tag not found in asset registry: V-GLV-523 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
+          <t>WARN: Tag not found in asset registry: V-NRV-1918 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD | FLOW: downstream</t>
         </is>
       </c>
       <c r="P51" s="8" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="Q51" s="13" t="inlineStr">
+        <v>0.773</v>
+      </c>
+      <c r="Q51" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -15187,512 +14556,8 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>V-GV-903</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>ISOLATION VALVE</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: V-GV-903 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="Q52" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>V-GV-91</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>GATE VALVE ON A HORIZONTAL LINE.</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: V-GV-91 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-      <c r="P53" s="8" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="Q53" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="R53" s="8" t="inlineStr">
-        <is>
-          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>V-GV-914</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>PIPING LINE</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: V-GV-914 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="Q54" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>V-GV-915</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>VALVE ON LINE</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: V-GV-915 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-      <c r="P55" s="8" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="Q55" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="R55" s="8" t="inlineStr">
-        <is>
-          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="n">
-        <v>185</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>V-GV-921</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>ON 1/2" LINE BRANCHING DOWN</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>GATE VALVE</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: V-GV-921 | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="Q56" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>MECHANICAL</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>V-NRV-1918</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>ON 12" LINE</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>CHECK VALVE</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>4224-MGDV-6-50-2004-001-C</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>MESAIEED GAS DISTRIBUTION STATIONS, MGDV | EPIC FOR UPGRADE OF ETHANE COMPRESSORS AT | STATION V AND ASSOCIATED FACILITIES AT STATION S | P&amp;ID – ETHANE GAS COMPRESSOR (K-V-201)</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>RE-ISSUED FOR CONSTRUCTION</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>29-08-24</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>WARN: Tag not found in asset registry: V-NRV-1918 | NO_SCOPE_DEFINITION_FOUND | NOT_IN_REGISTER | WITHIN_REVISION_CLOUD</t>
-        </is>
-      </c>
-      <c r="P57" s="8" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="Q57" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="R57" s="8" t="inlineStr">
-        <is>
-          <t>NOT_IN_REGISTER: tag not found in client asset register</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R57"/>
+  <autoFilter ref="A1:R51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15775,7 +14640,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18 10:46</t>
+          <t>2026-06-22 13:17</t>
         </is>
       </c>
     </row>
@@ -15793,7 +14658,7 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -15803,7 +14668,7 @@
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -15813,7 +14678,7 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -15840,7 +14705,7 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -15850,7 +14715,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -15860,7 +14725,7 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -15888,7 +14753,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -15900,7 +14765,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -15942,7 +14807,7 @@
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -15952,7 +14817,7 @@
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>0.638</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="30">
